--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92525</v>
+        <v>92526</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93346</v>
+        <v>93347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92526</v>
+        <v>92527</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93347</v>
+        <v>93348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>136054314</v>
       </c>
       <c r="B153" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136054315</v>
       </c>
       <c r="B154" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136054317</v>
       </c>
       <c r="B155" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>136054319</v>
       </c>
       <c r="B156" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>136054320</v>
       </c>
       <c r="B157" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136054295</v>
       </c>
       <c r="B159" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>136054394</v>
       </c>
       <c r="B160" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136054403</v>
       </c>
       <c r="B161" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92528</v>
+        <v>92534</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93349</v>
+        <v>93355</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>136054314</v>
       </c>
       <c r="B153" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136054315</v>
       </c>
       <c r="B154" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136054317</v>
       </c>
       <c r="B155" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>136054319</v>
       </c>
       <c r="B156" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>136054320</v>
       </c>
       <c r="B157" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136054295</v>
       </c>
       <c r="B159" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>136054394</v>
       </c>
       <c r="B160" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136054403</v>
       </c>
       <c r="B161" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>136054314</v>
       </c>
       <c r="B153" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136054315</v>
       </c>
       <c r="B154" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136054317</v>
       </c>
       <c r="B155" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>136054319</v>
       </c>
       <c r="B156" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>136054320</v>
       </c>
       <c r="B157" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136054295</v>
       </c>
       <c r="B159" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>136054394</v>
       </c>
       <c r="B160" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136054403</v>
       </c>
       <c r="B161" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92535</v>
+        <v>92541</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93356</v>
+        <v>93362</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92541</v>
+        <v>92548</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93362</v>
+        <v>93369</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>136054314</v>
       </c>
       <c r="B153" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136054315</v>
       </c>
       <c r="B154" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136054317</v>
       </c>
       <c r="B155" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>136054319</v>
       </c>
       <c r="B156" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>136054320</v>
       </c>
       <c r="B157" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136054295</v>
       </c>
       <c r="B159" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>136054394</v>
       </c>
       <c r="B160" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136054403</v>
       </c>
       <c r="B161" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92548</v>
+        <v>92549</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92549</v>
+        <v>92562</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93370</v>
+        <v>93383</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>136054314</v>
       </c>
       <c r="B153" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>136054315</v>
       </c>
       <c r="B154" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136054317</v>
       </c>
       <c r="B155" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>136054319</v>
       </c>
       <c r="B156" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>136054320</v>
       </c>
       <c r="B157" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136054295</v>
       </c>
       <c r="B159" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>136054394</v>
       </c>
       <c r="B160" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136054403</v>
       </c>
       <c r="B161" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136054270</v>
       </c>
       <c r="B6" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136054292</v>
       </c>
       <c r="B7" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136054306</v>
       </c>
       <c r="B8" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136054318</v>
       </c>
       <c r="B9" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136054325</v>
       </c>
       <c r="B10" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>136054328</v>
       </c>
       <c r="B11" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>136054356</v>
       </c>
       <c r="B12" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>136054371</v>
       </c>
       <c r="B13" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136054372</v>
       </c>
       <c r="B14" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136054373</v>
       </c>
       <c r="B15" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136054378</v>
       </c>
       <c r="B16" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136054414</v>
       </c>
       <c r="B17" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136054418</v>
       </c>
       <c r="B18" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136054435</v>
       </c>
       <c r="B19" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136054309</v>
       </c>
       <c r="B20" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136054323</v>
       </c>
       <c r="B21" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136054342</v>
       </c>
       <c r="B22" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92562</v>
+        <v>92563</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136054269</v>
       </c>
       <c r="B99" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>136054272</v>
       </c>
       <c r="B100" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>136054274</v>
       </c>
       <c r="B101" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>136054289</v>
       </c>
       <c r="B102" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>136054316</v>
       </c>
       <c r="B103" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>136054321</v>
       </c>
       <c r="B104" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>136054324</v>
       </c>
       <c r="B105" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>136054332</v>
       </c>
       <c r="B106" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>136054338</v>
       </c>
       <c r="B107" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>136054339</v>
       </c>
       <c r="B108" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>136054340</v>
       </c>
       <c r="B109" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>136054369</v>
       </c>
       <c r="B110" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>136054399</v>
       </c>
       <c r="B111" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>136054410</v>
       </c>
       <c r="B112" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>136054412</v>
       </c>
       <c r="B113" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>136054419</v>
       </c>
       <c r="B114" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>136054420</v>
       </c>
       <c r="B115" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>136054428</v>
       </c>
       <c r="B116" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>136054432</v>
       </c>
       <c r="B117" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>136054273</v>
       </c>
       <c r="B119" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>136054281</v>
       </c>
       <c r="B120" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>136054313</v>
       </c>
       <c r="B121" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>136054395</v>
       </c>
       <c r="B122" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>136054421</v>
       </c>
       <c r="B123" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>136054287</v>
       </c>
       <c r="B124" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>136054337</v>
       </c>
       <c r="B125" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>136054361</v>
       </c>
       <c r="B126" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>136054305</v>
       </c>
       <c r="B128" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>136054307</v>
       </c>
       <c r="B129" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>136054375</v>
       </c>
       <c r="B130" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>136054417</v>
       </c>
       <c r="B131" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>136054424</v>
       </c>
       <c r="B132" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>136054271</v>
       </c>
       <c r="B133" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>136054275</v>
       </c>
       <c r="B134" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>136054277</v>
       </c>
       <c r="B135" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>136054283</v>
       </c>
       <c r="B136" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>136054299</v>
       </c>
       <c r="B137" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>136054300</v>
       </c>
       <c r="B138" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>136054304</v>
       </c>
       <c r="B139" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>136054308</v>
       </c>
       <c r="B140" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>136054322</v>
       </c>
       <c r="B141" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>136054327</v>
       </c>
       <c r="B142" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>136054343</v>
       </c>
       <c r="B143" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>136054350</v>
       </c>
       <c r="B144" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>136054358</v>
       </c>
       <c r="B145" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>136054376</v>
       </c>
       <c r="B146" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>136054390</v>
       </c>
       <c r="B147" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>136054404</v>
       </c>
       <c r="B148" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>136054425</v>
       </c>
       <c r="B149" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>136054429</v>
       </c>
       <c r="B150" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>136054354</v>
       </c>
       <c r="B151" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>136054364</v>
       </c>
       <c r="B152" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>136054301</v>
       </c>
       <c r="B163" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>136054336</v>
       </c>
       <c r="B164" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>136054353</v>
       </c>
       <c r="B165" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>136054366</v>
       </c>
       <c r="B166" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>136054388</v>
       </c>
       <c r="B167" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>136054349</v>
       </c>
       <c r="B169" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>136054365</v>
       </c>
       <c r="B170" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
